--- a/data/trans_dic/P41C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,05</t>
+          <t>0,0; 9,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 4,5</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,7</t>
+          <t>0,72; 4,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,27</t>
+          <t>1,62; 4,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,8</t>
+          <t>1,25; 3,79</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 13,76</t>
+          <t>2,93; 13,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 12,58</t>
+          <t>5,32; 12,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,06; 11,24</t>
+          <t>5,09; 11,07</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,26</t>
+          <t>1,05; 5,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,73</t>
+          <t>3,08; 5,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,78</t>
+          <t>2,23; 4,74</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dificultades para tener un embarazo</t>
+          <t>Población con dificultades para tener un embarazo (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1886</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 3962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4617</t>
+          <t>0; 4145</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4492; 31631</t>
+          <t>4838; 30620</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7912; 19996</t>
+          <t>7596; 19767</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14815; 43373</t>
+          <t>14245; 43268</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4578; 21735</t>
+          <t>4625; 21142</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9834; 23006</t>
+          <t>9727; 23224</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17245; 38315</t>
+          <t>17356; 37734</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11166; 46217</t>
+          <t>9236; 46111</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21071; 39850</t>
+          <t>21409; 40083</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32861; 75203</t>
+          <t>35138; 74554</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41C_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P41C_R-Estudios-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,06</t>
+          <t>0,0; 8,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,55</t>
+          <t>2,21; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,22</t>
+          <t>1,78; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,79</t>
+          <t>2,3; 4,41</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 13,39</t>
+          <t>2,97; 13,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,7</t>
+          <t>4,65; 11,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 11,07</t>
+          <t>4,71; 10,69</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,24</t>
+          <t>2,64; 6,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,77</t>
+          <t>2,98; 5,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,74</t>
+          <t>3,18; 5,44</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1271</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3962</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4145</t>
+          <t>0; 5219</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>14644</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28752</t>
+          <t>31973</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4838; 30620</t>
+          <t>10346; 27772</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7596; 19767</t>
+          <t>9254; 22309</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14245; 43268</t>
+          <t>22710; 43461</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15374</t>
+          <t>15854</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25928</t>
+          <t>27081</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4625; 21142</t>
+          <t>5150; 24131</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9727; 23224</t>
+          <t>9474; 23676</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17356; 37734</t>
+          <t>17743; 40324</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>28556</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>29437</t>
+          <t>31769</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55929</t>
+          <t>60325</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9236; 46111</t>
+          <t>18331; 44366</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21409; 40083</t>
+          <t>23090; 42269</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35138; 74554</t>
+          <t>46634; 79938</t>
         </is>
       </c>
     </row>
